--- a/artfynd/A 61458-2023 artfynd.xlsx
+++ b/artfynd/A 61458-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61458-2023 artfynd.xlsx
+++ b/artfynd/A 61458-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92284958</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421032.3783867543</v>
+        <v>421032</v>
       </c>
       <c r="R2" t="n">
-        <v>6466430.489221031</v>
+        <v>6466430</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +748,9 @@
           <t>2021-04-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,7 +789,7 @@
         <v>92284962</v>
       </c>
       <c r="B3" t="n">
-        <v>100515</v>
+        <v>102304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421032.3783867543</v>
+        <v>421032</v>
       </c>
       <c r="R3" t="n">
-        <v>6466430.489221031</v>
+        <v>6466430</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +859,9 @@
           <t>2021-04-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 61458-2023 artfynd.xlsx
+++ b/artfynd/A 61458-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92284958</v>
+        <v>92282923</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Flågeberget - Område med mycket grov skog, Vg</t>
+          <t>Stora Flågeberget - N6733 - 1996 - Vissa naturvärden, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421032</v>
+        <v>421074</v>
       </c>
       <c r="R2" t="n">
-        <v>6466430</v>
+        <v>6466480</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Blandskog och rasbrant</t>
+          <t>Rasbrant och lövskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92284962</v>
+        <v>92284958</v>
       </c>
       <c r="B3" t="n">
-        <v>102326</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -890,6 +880,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>92284962</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stora Flågeberget - Område med mycket grov skog, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>421032</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6466430</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bolum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Blandskog och rasbrant</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Billingens flora</t>
         </is>
